--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -32,6 +32,9 @@
       <family val="2"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -56,7 +59,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -65,6 +68,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,156 +450,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="31.59765625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="13.69921875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="36.5" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
     <col width="8.796875" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>itemId</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>itemName</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>item.weapon.greatsword.basic</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>기본 대검</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>평범한 대검입니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>item.weapon.shotgun.flamethrower</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>불꽃 분사기</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>불꽃을 여러갈래로 쏘아댑니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>item.armor.helmet.basic</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>기본 투구</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>평범한 투구입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>item.armor.chest.sturdy</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>견고한 갑옷</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>튼튼한 갑옷입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>item.armor.boots.ninja_movement</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>닌자의 움직임</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>양산형 신발입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>item.armor.boots.quantum_shoes</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>퀀텀 슈즈</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>하이-테크놀로지가 탑재된 신발입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>item.potion.red</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>빨간 물약</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>포션입니다.</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -609,142 +609,142 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="31.59765625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16.69921875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="36.5" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="22" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="40" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>itemId</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>itemName</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>item.weapon.greatsword.basic</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Basic Greatsword</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>An ordinary greatsword.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>item.weapon.shotgun.flamethrower</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Flamethrower</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sprays flames in multiple directions.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>item.armor.helmet.basic</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Basic Helmet</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>An ordinary helmet.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>item.armor.chest.sturdy</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Sturdy Armor</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>A tough suit of armor.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>item.armor.boots.ninja_movement</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ninja's Movement</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Mass-produced footwear.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>item.armor.boots.quantum_shoes</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Quantum Shoes</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Footwear equipped with high technology.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>item.potion.red</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Red Potion</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>A potion.</t>
         </is>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -477,123 +477,149 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>item.weapon.greatsword.basic</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>기본 대검</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>평범한 대검입니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>item.weapon.shotgun.flamethrower</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>불꽃 분사기</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>불꽃을 여러갈래로 쏘아댑니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>item.armor.helmet.basic</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>기본 투구</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>평범한 투구입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>item.armor.chest.sturdy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>견고한 갑옷</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>튼튼한 갑옷입니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>item.armor.boots.ninja_movement</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>닌자의 움직임</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>양산형 신발입니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>item.armor.boots.quantum_shoes</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>퀀텀 슈즈</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>하이-테크놀로지가 탑재된 신발입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>item.potion.red</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>빨간 물약</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>포션입니다.</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>item.relic.mass-produced_core</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>양산형 코어</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>item.relic.advanced_core</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>고급 코어</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -606,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -632,123 +658,149 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>item.weapon.greatsword.basic</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Basic Greatsword</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>An ordinary greatsword.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>item.weapon.shotgun.flamethrower</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Flamethrower</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>Sprays flames in multiple directions.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>item.armor.helmet.basic</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Basic Helmet</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>An ordinary helmet.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>item.armor.chest.sturdy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Sturdy Armor</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>A tough suit of armor.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>item.armor.boots.ninja_movement</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Ninja's Movement</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>Mass-produced footwear.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>item.armor.boots.quantum_shoes</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>Quantum Shoes</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>Footwear equipped with high technology.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>item.potion.red</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>Red Potion</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>A potion.</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>item.relic.mass-produced_core</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mass-Produced Core</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>item.relic.advanced_core</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Advanced Core</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7863AD3-8CEF-48F6-9F67-9888A9B816D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69C9150-3B42-4BC9-81ED-3267723FE0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-192" yWindow="3456" windowWidth="23232" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7140" yWindow="1692" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>itemId</t>
   </si>
@@ -161,6 +161,50 @@
   <si>
     <t>보통의 코어보다 출력이 높은 코어입니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.potion.red</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.mechanicaldestroyer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.treebranch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계 파괴자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나뭇가지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>길거리에 굴러다닐 법한 나뭇가지입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단단한 기계들을 무자비하게 파괴할 수 있는 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mechanical Destroyer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Branch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A weapon capable of mercilessly destroying even the toughest machines.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A stick you could easily find lying on the ground.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -542,12 +586,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -585,79 +629,101 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
+      <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -669,12 +735,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -711,77 +777,99 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
+      <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
+      <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9"/>
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>43</v>
       </c>
-      <c r="C10"/>
+      <c r="C12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R91b3020b69114a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R73eff04d1f384a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R23c16ec52ccc4622"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R30d45a6c27de4bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rf3905928b4b94331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rc68d9079a6cd4ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R3dffc582f1ef4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R3c1467092506449b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -482,6 +482,94 @@
         <x:v>보통의 코어보다 출력이 높은 코어입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>item.weapon.blunt.noentrysign</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>진입 금지 표지판</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>히히 못가</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>item.weapon.axe.icecrusher</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>아이스 크러셔</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>강력한 냉기를 품은 도끼입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>item.weapon.axe.inferno</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>인페르노</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>이 도끼가 품은 화염은 적에게 지옥을 선사합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>item.weapon.blunt.baseballbat</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>빠따</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>야구 빠따를 전투용으로 개조했습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>item.weapon.blunt.lightsaber</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>라이트세이버</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>광선검입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>item.weapon.greatsword.crusader</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>크루세이더</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>성스러운 일격을 날릴 수 있는 대검입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>item.weapon.greatsword.guardiansjustice</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>수호자의 정의</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>정의는 승리한다!</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>item.weapon.blunt.ironpipe</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>쇠 파이프</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>고철 처리장에서 가져온 녹 슨 파이프입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -628,6 +716,94 @@
         <x:v>A core with higher output than an ordinary one.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>item.weapon.blunt.noentrysign</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>No Entry Sign</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Hehe, no entry.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>item.weapon.axe.icecrusher</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Ice Crusher</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>A mighty axe imbued with intense cold.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>item.weapon.axe.inferno</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Inferno</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>The flames within this axe bring hell to its enemies.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>item.weapon.blunt.baseballbat</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Baseball Bat</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>A baseball bat modified for combat.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>item.weapon.blunt.lightsaber</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Lightsaber</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>A lightsaber.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>item.weapon.greatsword.crusader</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Crusader</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>A greatsword capable of delivering a holy strike.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>item.weapon.greatsword.guardiansjustice</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Guardian's Justice</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Justice always prevails!</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>item.weapon.blunt.ironpipe</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Iron Pipe</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>A rusty pipe taken from a scrapyard.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -774,6 +950,94 @@
         <x:v>通常のコアより出力が高いコアです。</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>item.weapon.blunt.noentrysign</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>進入禁止標識</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>へへっ、通行禁止だ。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>item.weapon.axe.icecrusher</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>アイスクラッシャー</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>強烈な冷気を宿した斧です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>item.weapon.axe.inferno</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>インフェルノ</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>この斧に宿る炎は、敵に地獄をもたらします。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>item.weapon.blunt.baseballbat</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>野球バット</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>野球のバットを戦闘用に改造しました。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>item.weapon.blunt.lightsaber</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>ライトセーバー</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>ライトセーバーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>item.weapon.greatsword.crusader</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>クルセイダー</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>聖なる一撃を放てる大剣です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>item.weapon.greatsword.guardiansjustice</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>守護者の正義</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>正義は必ず勝つ！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>item.weapon.blunt.ironpipe</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>鉄パイプ</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>廃品処理場から持ってきた錆びた鉄パイプです。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -920,6 +1184,94 @@
         <x:v>输出比普通核心更高的核心。</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>item.weapon.blunt.noentrysign</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>禁止进入标志牌</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>嘿嘿，此路不通。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>item.weapon.axe.icecrusher</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>冰霜粉碎者</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>一把蕴含强大寒气的斧头。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>item.weapon.axe.inferno</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>炼狱</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>这把斧头中蕴藏的烈焰会将地狱带给敌人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>item.weapon.blunt.baseballbat</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>棒球棍</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>将棒球棍改造成了战斗武器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>item.weapon.blunt.lightsaber</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>光剑</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>这是一把光剑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>item.weapon.greatsword.crusader</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>十字军</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>一把能够施展神圣一击的大剑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>item.weapon.greatsword.guardiansjustice</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>守护者的正义</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>正义必胜！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>item.weapon.blunt.ironpipe</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>铁管</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>从废料场捡来的生锈铁管。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -647,6 +647,23 @@
       <c r="C10" s="0" t="inlineStr">
         <is>
           <t>보통의 코어보다 출력이 높은 코어입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>item.relic.cybernetic_core</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>사이버네틱 코어</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>신경계에 직접 연결되는 강화 코어입니다.</t>
         </is>
       </c>
     </row>
@@ -661,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="32" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -836,6 +853,23 @@
       <c r="C10" s="0" t="inlineStr">
         <is>
           <t>A core with higher output than an ordinary one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>item.relic.cybernetic_core</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cybernetic Core</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>An augmentation core wired directly into the nervous system.</t>
         </is>
       </c>
     </row>
@@ -850,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="1" min="1" max="1"/>
@@ -1025,6 +1059,23 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>通常のコアより出力が高いコアです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>item.relic.cybernetic_core</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>サイバネティックコア</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>神経系に直接接続される強化コアです。</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="1" min="1" max="1"/>
@@ -1217,6 +1268,23 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>item.relic.cybernetic_core</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>赛博核心</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>直接连接神经系统的强化核心。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rfbc9b2e57ab14a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rcacdffc5fd8045c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R14e09a58ee7f48c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rac7964675ec441ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Red42a0eb567b45d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rbdf08d0b6cd44901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="Rd044e4f1b9d9425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R0fcae0be98ca49fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -581,6 +581,50 @@
         <x:v>신경계에 직접 연결되는 강화 코어입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>item.weapon.greatsword.energyblade</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>에너지 블레이드</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>E=mc². 이 검은 그 공식이 얼마나 위험한지 가장 조용하게 증명한다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>item.weapon.greatsword.zeroblade</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>제로 블레이드</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>절대영도에 가까운 냉각장을 방출합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>item.weapon.greatsword.solarblade</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>솔라 블레이드</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>태양의 핵융합을 모방한 플라즈마 칼날.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>item.weapon.greatsword.voltblade</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>볼트 블레이드</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>수백만 볼트의 전위를 한 줄기로 압축했습니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -826,6 +870,50 @@
         <x:v>An augmentation core wired directly into the nervous system.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>item.weapon.greatsword.energyblade</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Energy Blade</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>E=mc². This blade quietly proves just how dangerous that equation can be.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>item.weapon.greatsword.zeroblade</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Zero Blade</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Emits a cooling field approaching absolute zero.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>item.weapon.greatsword.solarblade</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Solar Blade</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>A plasma blade modeled after the Sun's nuclear fusion.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>item.weapon.greatsword.voltblade</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Volt Blade</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Compresses millions of volts of electric potential into a single edge.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1071,6 +1159,50 @@
         <x:v>神経系に直接接続される強化コアです。</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>item.weapon.greatsword.energyblade</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>エネルギーブレード</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>E=mc²。この剣は、その公式がどれほど危険かを静かに証明する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>item.weapon.greatsword.zeroblade</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>ゼロブレード</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>絶対零度に近い冷却場を放出します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>item.weapon.greatsword.solarblade</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>ソーラーブレード</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>太陽の核融合を模倣したプラズマブレードです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>item.weapon.greatsword.voltblade</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>ボルトブレード</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>数百万ボルトの電位を一本の刃に圧縮しました。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1316,6 +1448,50 @@
         <x:v>直接连接神经系统的强化核心。</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>item.weapon.greatsword.energyblade</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>能量之刃</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>E=mc²。这把剑悄无声息地证明了这个公式究竟有多危险。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>item.weapon.greatsword.zeroblade</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>零度之刃</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>释放接近绝对零度的冷却场。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>item.weapon.greatsword.solarblade</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>太阳之刃</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>模仿太阳核聚变的等离子体刀刃。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>item.weapon.greatsword.voltblade</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>伏特之刃</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>将数百万伏特的电势压缩成一道刀锋。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48036C1-0DB4-4E55-83B5-4BA6BFC83948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA4FDA6-6052-4D2D-8031-6DBF77C8C741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="1092" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="238">
   <si>
     <t>itemId</t>
   </si>
@@ -740,12 +740,67 @@
   <si>
     <t>デブリスの心核</t>
   </si>
+  <si>
+    <t>item.weapon.wasteheatcleaver</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐열 절단 대검</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A massive blade that concentrates waste heat along its edge, allowing it to cut through even the toughest machinery.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wasteheat Cleaver</t>
+  </si>
+  <si>
+    <t>廃熱断裁大剣</t>
+  </si>
+  <si>
+    <t>刃に廃熱を集中させ、強固な機械すら断ち切る大剣。</t>
+  </si>
+  <si>
+    <t>废热断裁巨剑</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>将</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>废热汇聚于剑刃之上，连坚固的机械也能轻易斩断。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 칼날은 폐열을 가장자리에 집중시켜 견고한 기계도 절단할 수 있게 해줍니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.wasteheatcleaver</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,6 +847,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -820,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -841,6 +903,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1053,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -1348,6 +1411,17 @@
         <v>221</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1356,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
@@ -1650,6 +1724,17 @@
         <v>222</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1658,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -1952,6 +2037,17 @@
         <v>224</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1960,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -2254,6 +2350,17 @@
         <v>225</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.45">
+      <c r="A27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA4FDA6-6052-4D2D-8031-6DBF77C8C741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB74EEA-8E42-4EE2-AF1D-D47139C1EE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="1092" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="327">
   <si>
     <t>itemId</t>
   </si>
@@ -795,12 +795,386 @@
     <t>item.weapon.greatsword.wasteheatcleaver</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>item.weapon.axe.wildfire</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>와일드파이어</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.thighbone</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.superrefrigerant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>초냉매</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.morningstar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침의 별</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.magicstaff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법(물리) 지팡이</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.nightsword</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤의 칼날</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.rusty</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹슨 대검</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>꺼지지 않는 불씨를 품은 도끼입니다. 휘두를 때마다 잠들어 있던 열기가 다시 타오릅니다.</t>
+  </si>
+  <si>
+    <t>우주 괴물 대퇴골</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>새벽하늘에서 가장 밝게 빛나는 별의 이름을 가진 무기입니다. 맞은 사람도 잠시 별을 볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>마력이 없어도 사용할 수 있는 마법 지팡이입니다. 주문은 간단합니다. 힘껏 휘두르세요.</t>
+  </si>
+  <si>
+    <t>녹이 슬고 날도 무뎌진 낡은 대검입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛을 삼킨 듯 검게 물든 대검입니다. 어둠 속에서는 칼날의 경계조차 흐릿해집니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>정체불명의 우주 괴물에게서 나온 대퇴골입니다. 뼈라고 믿기 어려울 만큼 무겁고 단단합니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>극저온의 냉매가 봉인되어 있습니다. 충격을 받을 때마다 주변의 열을 무자비하게 빼앗습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ワイルドファイア</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>消えることのない火種を宿した斧。振るうたび、眠っていた熱が再び燃え上がる。</t>
+  </si>
+  <si>
+    <t>宇宙怪物の大腿骨</t>
+  </si>
+  <si>
+    <t>正体不明の宇宙怪物から取れた大腿骨。骨とは思えないほど重く、頑丈だ。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>極低温の冷媒が封じ込められている。衝撃を受けるたび、周囲の熱を容赦なく奪い取る。</t>
+  </si>
+  <si>
+    <t>超冷媒</t>
+  </si>
+  <si>
+    <t>明けの明星</t>
+  </si>
+  <si>
+    <t>魔法（物理）の杖</t>
+  </si>
+  <si>
+    <t>夜の刃</t>
+  </si>
+  <si>
+    <r>
+      <t>錆びた大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>剣</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>明け方の空で最も明るく輝く星の名を持つ武器。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>殴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>られた相手も、しばらく星を見ることになる。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力がなくても使える魔法の杖。呪文は簡単だ。力いっぱい振り回せ。</t>
+  </si>
+  <si>
+    <t>光を飲み込んだかのように黒く染まった大剣。闇の中では、その刃の境界すら曖昧になる。</t>
+  </si>
+  <si>
+    <t>錆びつき、刃も鈍った古い大剣。この重さなら、別に鋭くなくても問題ない。</t>
+  </si>
+  <si>
+    <t>WildFire</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thighbone</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super Refrigerant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic (Physical) Staff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Night Sword</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rusty GreatSword</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>An axe that holds an undying ember. With every swing, its dormant heat flares to life.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The femur of an unidentified space monster. It's far heavier and tougher than any bone has a right to be.</t>
+  </si>
+  <si>
+    <t>Contains a cryogenic refrigerant. Every impact mercilessly drains heat from its surroundings.</t>
+  </si>
+  <si>
+    <t>A weapon named after the brightest star of the dawn. Its victims may see a few stars of their own.</t>
+  </si>
+  <si>
+    <t>Morning Star</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A magic staff that requires no mana. The incantation is simple: swing it as hard as you can.</t>
+  </si>
+  <si>
+    <t>A greatsword blackened as though it had swallowed the light. In darkness, even the edge becomes difficult to discern.</t>
+  </si>
+  <si>
+    <t>An old greatsword, rusted and dull.</t>
+  </si>
+  <si>
+    <t>野火</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>一把蕴藏着不灭火种的斧头。每次挥动，沉睡的热量都会再次燃起。</t>
+  </si>
+  <si>
+    <t>宇宙怪物股骨</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>来自不明宇宙怪物的股骨。它沉重而坚硬，完全不像普通的骨头。</t>
+  </si>
+  <si>
+    <t>内部封存着超低温冷媒。每次受到冲击，都会毫不留情地夺走周围的热量。</t>
+  </si>
+  <si>
+    <t>晨星</t>
+  </si>
+  <si>
+    <t>以黎明时最明亮的星辰命名的武器。被它击中的人，大概也能看见几颗星星。</t>
+  </si>
+  <si>
+    <t>魔法（物理）杖</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>一根不需要魔力也能使用的魔法杖。咒语很简单：用力挥下去。</t>
+  </si>
+  <si>
+    <t>夜之刃</t>
+  </si>
+  <si>
+    <t>锈蚀大剑</t>
+  </si>
+  <si>
+    <t>一把仿佛吞噬了光芒般漆黑的大剑。在黑暗中，就连剑刃的轮廓也会变得模糊。</t>
+  </si>
+  <si>
+    <t>一把锈迹斑斑、剑刃也已经变钝的旧大剑。不过有这种重量，锋不锋利似乎也没那么重要。</t>
+  </si>
+  <si>
+    <t>item.armor.boots.discardedboostermodule</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐기된 부스터 모듈</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.armor.helmet.signaljammer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>군집 신호 교란기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.armor.chest.solargrace</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양의 은혜</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐기된 기동 로봇에서 떼어낸 부스터 모듈입니다. 안전 기준은 충족하지 못했지만, 속도 기준은 확실히 충족합니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변의 군집 통신 신호에 잡음을 섞어 넣는 장치입니다. 적들은 혼란스러워지고, 착용자는 머리가 조금 아파집니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양 에너지를 흡수해 착용자를 보호하는 갑옷입니다. 별 하나가 보내는 은혜치고는 꽤나 뜨겁습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discarded Booster Module</t>
+  </si>
+  <si>
+    <t>A booster module salvaged from discarded mobility gear. It failed the safety standards, but certainly not the speed standards.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swarm Signal Jammer</t>
+  </si>
+  <si>
+    <t>A device that injects random noise into nearby swarm communication signals. It confuses the enemy and gives the wearer a slight headache.</t>
+  </si>
+  <si>
+    <t>Armor that absorbs solar energy to protect its wearer. For a blessing from a star, it's surprisingly hot.</t>
+  </si>
+  <si>
+    <t>Solar Grace</t>
+  </si>
+  <si>
+    <t>廃棄されたブースターモジュール</t>
+  </si>
+  <si>
+    <t>群体信号ジャマー</t>
+  </si>
+  <si>
+    <t>太陽の恩寵</t>
+  </si>
+  <si>
+    <t>廃棄された機動装備から取り外したブースターモジュール。安全基準は満たしていないが、速度に関しては文句なしだ。</t>
+  </si>
+  <si>
+    <t>周囲の群体通信信号にランダムなノイズを混ぜ込む装置。敵は混乱し、装着者は少し頭が痛くなる。</t>
+  </si>
+  <si>
+    <t>太陽エネルギーを吸収し、装着者を守る鎧。星から授かる恩寵にしては、かなり熱い。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>废</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>弃助推模</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>块</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群信号干扰器</t>
+  </si>
+  <si>
+    <t>太阳恩赐</t>
+  </si>
+  <si>
+    <t>从废弃机动装备上拆下的助推模块。虽然没能达到安全标准，但速度绝对达标。</t>
+  </si>
+  <si>
+    <t>向周围的集群通信信号中注入随机噪声的装置。敌人会陷入混乱，佩戴者则可能有点头疼。</t>
+  </si>
+  <si>
+    <t>吸收太阳能量来保护穿戴者的装甲。作为一颗恒星赐予的恩惠，它还真是相当烫手。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,6 +1228,20 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -882,7 +1270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -904,6 +1292,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1116,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -1422,6 +1816,116 @@
         <v>236</v>
       </c>
     </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1430,11 +1934,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="66" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1733,6 +2237,116 @@
       </c>
       <c r="C27" s="6" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -1743,11 +2357,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.69921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2046,6 +2660,116 @@
       </c>
       <c r="C27" s="7" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2056,7 +2780,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -2361,6 +3085,116 @@
         <v>235</v>
       </c>
     </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB74EEA-8E42-4EE2-AF1D-D47139C1EE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E670AC86-171B-49B0-9441-3D8EEDD91592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="372">
   <si>
     <t>itemId</t>
   </si>
@@ -1168,6 +1168,146 @@
   </si>
   <si>
     <t>吸收太阳能量来保护穿戴者的装甲。作为一颗恒星赐予的恩惠，它还真是相当烫手。</t>
+  </si>
+  <si>
+    <t>item.weapon.axe.phaseharvester</t>
+  </si>
+  <si>
+    <t>공허의 수확자</t>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.arcblade</t>
+  </si>
+  <si>
+    <t>아크 블레이드</t>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.corebreaker</t>
+  </si>
+  <si>
+    <t>코어 브레이커</t>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.chainsaw</t>
+  </si>
+  <si>
+    <t>체인소</t>
+  </si>
+  <si>
+    <t>item.weapon.blunt.shovel</t>
+  </si>
+  <si>
+    <t>강제 정비 도구</t>
+  </si>
+  <si>
+    <t>공허 에너지를 칼날 형태로 압축한 전투용 낫입니다. 한 번 휘두를 때마다 보랏빛 궤적이 공간과 장갑을 함께 베어냅니다.</t>
+  </si>
+  <si>
+    <t>검신을 따라 고전압 전류를 순환시키는 전투용 도검입니다. 절단면으로 방전된 전류가 내부 회로까지 파고듭니다.</t>
+  </si>
+  <si>
+    <t>중앙 동력핵의 출력을 검신 전체에 방출하는 대형 병기입니다. 외장갑을 부수는 것은 시작일 뿐, 진짜 목표는 그 안쪽의 동력 코어입니다.</t>
+  </si>
+  <si>
+    <t>폐기 로봇의 장갑을 절단하기 위해 만들어진 산업용 공구입니다. 전쟁터에서는 굳이 폐기 판정을 기다릴 필요가 없다는 사실이 밝혀졌습니다.</t>
+  </si>
+  <si>
+    <t>야전 정비반에서 사용하던 다목적 중장비입니다. 정상적인 정비 절차로 해결되지 않는 기계는 충분한 운동에너지를 가하면 대개 조용해집니다.</t>
+  </si>
+  <si>
+    <t>Phasae Harvester</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arc Blade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChainSaw</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shovel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A heavy cutting weapon that projects a high-frequency phase field along its blade. Even reinforced armor becomes fragile when its molecular bonds begin to destabilize.</t>
+  </si>
+  <si>
+    <t>高周波の位相フィールドを刃状に展開する大型切断兵器。どれほど頑丈な装甲も、分子結合が揺らぐ瞬間だけは脆くなる。</t>
+  </si>
+  <si>
+    <t>将高频相位场展开为刀刃的大型切割兵器。再坚固的装甲，在分子键动摇的瞬间也会变得脆弱。</t>
+  </si>
+  <si>
+    <t>相位收割器</t>
+  </si>
+  <si>
+    <t>位相収穫機</t>
+  </si>
+  <si>
+    <t>アークブレード</t>
+  </si>
+  <si>
+    <t>电弧刃</t>
+  </si>
+  <si>
+    <t>A combat blade that circulates high-voltage current along its edge. Electricity discharged through the cut can reach circuitry deep inside the target.</t>
+  </si>
+  <si>
+    <t>刀身に沿って高電圧電流を循環させる戦闘用ブレード。切断面から放電し、標的内部の回路まで焼き切る。</t>
+  </si>
+  <si>
+    <t>让高压电流沿刀身循环的战斗刀刃。电流会从切口放电，并侵入目标内部的电路。</t>
+  </si>
+  <si>
+    <t>Corebreaker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>コアブレイカー</t>
+  </si>
+  <si>
+    <t>装甲解体ソー</t>
+  </si>
+  <si>
+    <t>強制整備ツール</t>
+  </si>
+  <si>
+    <t>A heavy weapon that releases the output of its central power core across the blade on impact. Breaking the outer armor is only the first step—the real target is the power core beneath it.</t>
+  </si>
+  <si>
+    <t>An industrial saw designed to cut apart the armor of decommissioned robots. Battlefield testing revealed that waiting for official decommissioning was entirely optional.</t>
+  </si>
+  <si>
+    <t>A multipurpose heavy tool once used by field maintenance crews. Machines that resist conventional repairs tend to become quiet after sufficient kinetic energy is applied.</t>
+  </si>
+  <si>
+    <t>衝突の瞬間、中央動力コアの出力を刀身全体へ放出する大型兵器。外装を砕くのは前座にすぎない。本命はその奥の動力コアだ。</t>
+  </si>
+  <si>
+    <t>廃棄されたロボットの装甲を切断するための産業用工具。戦場では、正式な廃棄判定を待つ必要がないことが判明した。</t>
+  </si>
+  <si>
+    <t>野戦整備班で使用されていた多目的重工具。通常の整備で直らない機械も、十分な運動エネルギーを与えれば大抵は静かになる。</t>
+  </si>
+  <si>
+    <t>核心破坏者</t>
+  </si>
+  <si>
+    <t>装甲拆解锯</t>
+  </si>
+  <si>
+    <t>强制维修工具</t>
+  </si>
+  <si>
+    <t>在撞击瞬间将中央动力核心的输出释放至整个剑身的重型兵器。击碎外部装甲只是第一步，真正的目标是藏在里面的动力核心。</t>
+  </si>
+  <si>
+    <t>原本用于切割报废机器人装甲的工业工具。后来人们发现，在战场上其实没必要等它们正式报废。</t>
+  </si>
+  <si>
+    <t>曾由战地维修人员使用的多用途重型工具。正常维修无法解决的机器，只要施加足够的动能，通常都会安静下来。</t>
   </si>
 </sst>
 </file>
@@ -1292,10 +1432,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1510,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -1900,7 +2040,7 @@
       <c r="B35" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>306</v>
       </c>
     </row>
@@ -1911,7 +2051,7 @@
       <c r="B36" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>307</v>
       </c>
     </row>
@@ -1922,8 +2062,63 @@
       <c r="B37" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +2129,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -2349,6 +2544,61 @@
         <v>313</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2357,7 +2607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -2772,6 +3022,61 @@
         <v>320</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2780,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -3166,7 +3471,7 @@
       <c r="A35" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>321</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -3193,6 +3498,61 @@
       </c>
       <c r="C37" s="7" t="s">
         <v>326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E670AC86-171B-49B0-9441-3D8EEDD91592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A5CBEC-FC58-41D8-9CA1-3C129A91A950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="453">
   <si>
     <t>itemId</t>
   </si>
@@ -73,12 +73,6 @@
     <t>item.armor.helmet.basic</t>
   </si>
   <si>
-    <t>기본 투구</t>
-  </si>
-  <si>
-    <t>평범한 투구입니다.</t>
-  </si>
-  <si>
     <t>item.armor.chest.sturdy</t>
   </si>
   <si>
@@ -94,9 +88,6 @@
     <t>닌자의 움직임</t>
   </si>
   <si>
-    <t>양산형 신발입니다.</t>
-  </si>
-  <si>
     <t>item.armor.boots.quantum_shoes</t>
   </si>
   <si>
@@ -253,9 +244,6 @@
     <t>Ninja's Movement</t>
   </si>
   <si>
-    <t>Mass-produced footwear.</t>
-  </si>
-  <si>
     <t>Quantum Shoes</t>
   </si>
   <si>
@@ -373,9 +361,6 @@
     <t>忍者の動き</t>
   </si>
   <si>
-    <t>量産型の靴です。</t>
-  </si>
-  <si>
     <t>クァンタムシューズ</t>
   </si>
   <si>
@@ -491,9 +476,6 @@
   </si>
   <si>
     <t>忍者之动</t>
-  </si>
-  <si>
-    <t>量产型鞋子。</t>
   </si>
   <si>
     <t>量子鞋</t>
@@ -1309,12 +1291,561 @@
   <si>
     <t>曾由战地维修人员使用的多用途重型工具。正常维修无法解决的机器，只要施加足够的动能，通常都会安静下来。</t>
   </si>
+  <si>
+    <t>Improvised Headguard</t>
+  </si>
+  <si>
+    <t>item.armor.helmet.improvisedheadguard</t>
+  </si>
+  <si>
+    <t>item.armor.chest.woodenarmor</t>
+  </si>
+  <si>
+    <t>item.armor.helmet.steelheadguard</t>
+  </si>
+  <si>
+    <t>item.armor.chest.steelarmor</t>
+  </si>
+  <si>
+    <t>급조 머리 보호대</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 갑옷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>철판 보호대</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>철판 갑옷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변에서 구한 재료를 엮어 만든 임시 보호구입니다. 믿음직스럽진 않지만, 맨머리보다는 낫습니다.</t>
+  </si>
+  <si>
+    <t>여러 장의 목재를 이어 붙여 만든 갑옷입니다. 총알을 막기엔 부족하지만, 가벼운 충격 정도는 받아낼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>얇은 철판을 머리 형태에 맞춰 이어 붙인 보호구입니다. 급조품보다 무겁지만, 그만큼 훨씬 단단합니다.</t>
+  </si>
+  <si>
+    <t>여러 겹의 철판을 겹쳐 만든 단순한 갑옷입니다. 로봇의 공격을 정면으로 받아낼 여유가 조금 생깁니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simple armor constructed from overlapping steel plates. It offers a better chance of taking a robot's attack head-on.</t>
+  </si>
+  <si>
+    <t>鉄板を何枚も重ねて作った単純な防具。ロボットの攻撃を正面から受け止める余裕が少し増える。</t>
+  </si>
+  <si>
+    <t>由多层钢板叠合而成的简单护甲。面对机器人的正面攻击时，多少更有底气。</t>
+  </si>
+  <si>
+    <t>Wooden Armor</t>
+  </si>
+  <si>
+    <t>Steel Headguard</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steel Armor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A makeshift headguard assembled from whatever materials were available. It is not exactly reliable, but it beats having no protection at all.</t>
+  </si>
+  <si>
+    <t>Armor made by fastening several wooden plates together. It will not stop much firepower, but it can soften lighter impacts.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A headguard made from thin steel plates fitted around the head. Heavier than improvised gear, but considerably tougher.</t>
+  </si>
+  <si>
+    <t>即席ヘッドガード</t>
+  </si>
+  <si>
+    <t>木製アーマー</t>
+  </si>
+  <si>
+    <t>鉄板ヘッドガード</t>
+  </si>
+  <si>
+    <t>鉄板アーマー</t>
+  </si>
+  <si>
+    <t>手近な材料を寄せ集めて作った即席の防具。頼りないが、何も被らないよりはましだ。</t>
+  </si>
+  <si>
+    <t>何枚もの木板をつなぎ合わせて作った防具。強力な攻撃には心許ないが、軽い衝撃なら多少は受け止められる。</t>
+  </si>
+  <si>
+    <t>薄い鉄板を頭の形に合わせて組み上げた防具。即席装備より重いが、そのぶん頑丈だ。</t>
+  </si>
+  <si>
+    <t>简易头部护具</t>
+  </si>
+  <si>
+    <t>木制护甲</t>
+  </si>
+  <si>
+    <t>钢板头部护具</t>
+  </si>
+  <si>
+    <t>钢板护甲</t>
+  </si>
+  <si>
+    <t>用随手找到的材料拼凑而成的临时护具。虽然谈不上可靠，但总比毫无防护要强。</t>
+  </si>
+  <si>
+    <r>
+      <t>用多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>木板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>拼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>接而成的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>护</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>甲。面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>强力攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>击并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>不可靠，但多少能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>缓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>冲一些</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>轻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>微冲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将薄钢板按照头部形状拼接而成的护具。虽然比临时装备更重，但也坚固得多。</t>
+  </si>
+  <si>
+    <t>item.armor.helmet.cauldronhelmet</t>
+  </si>
+  <si>
+    <t>가마솥 투구</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>두꺼운 금속 가마솥을 머리에 뒤집어쓴 투구입니다. 원래 용도보다 지금이 더 잘 어울리는 것 같습니다.</t>
+  </si>
+  <si>
+    <t>Cauldron Helmet</t>
+  </si>
+  <si>
+    <t>A helmet made by wearing a thick metal cauldron upside down. Somehow, it seems better suited to this purpose than its original one.</t>
+  </si>
+  <si>
+    <t>大釜の兜</t>
+  </si>
+  <si>
+    <t>大锅头盔</t>
+  </si>
+  <si>
+    <t>分厚い金属製の大釜を頭にかぶった兜。本来の用途より、今の使い方のほうが似合っている気がする。</t>
+  </si>
+  <si>
+    <t>把厚重的金属大锅倒扣在头上制成的头盔。总觉得现在的用途比原本的用途更适合它。</t>
+  </si>
+  <si>
+    <t>item.armor.chest.basic</t>
+  </si>
+  <si>
+    <t>item.armor.boots.basic</t>
+  </si>
+  <si>
+    <t>item.armor.boots.lightweight</t>
+  </si>
+  <si>
+    <t>item.armor.boots.poweredassist</t>
+  </si>
+  <si>
+    <t>기본 옷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 부츠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>경량 안전화</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>동력 보조 부츠</t>
+  </si>
+  <si>
+    <t>평범한 옷입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 부츠입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">불필요한 보호판을 제거해 무게를 줄인 작업용 안전화입니다. </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소형 구동기가 착용자의 이동을 보조하는 작업용 부츠입니다. 무거운 짐을 나르기 위해 만들어졌지만, 빠르게 움직일 때도 꽤 유용합니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설적인 닌자의 움직임을 재현하도록 설계된 특수 전투화입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 헬멧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 헬멧입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Armor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Powered Assist Boots</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lightweight Safety Boots</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Boots</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>An ordinary boots.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>An ordinary armor.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Work boots lightened by removing unnecessary protective plates.</t>
+  </si>
+  <si>
+    <t>Work boots equipped with compact actuators that assist the wearer's steps. Designed for carrying heavy loads, they also work surprisingly well for moving quickly.</t>
+  </si>
+  <si>
+    <t>Specialized combat footwear designed to reproduce the footwork of a legendary ninja.</t>
+  </si>
+  <si>
+    <t>基本アーマー</t>
+  </si>
+  <si>
+    <t>基本ブーツ</t>
+  </si>
+  <si>
+    <t>ごく普通の防具。</t>
+  </si>
+  <si>
+    <t>ごく普通のブーツ。</t>
+  </si>
+  <si>
+    <t>基础护甲</t>
+  </si>
+  <si>
+    <t>基础靴</t>
+  </si>
+  <si>
+    <t>一件普通的护甲。</t>
+  </si>
+  <si>
+    <t>一双普通的靴子。</t>
+  </si>
+  <si>
+    <t>伝説の忍が見せた足運びを再現するために設計された特殊戦闘靴。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>重</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>现传说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>中忍者的身法而</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>设计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>的特殊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>战</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>斗靴。</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>轻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>型安全靴</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>动力辅助靴</t>
+  </si>
+  <si>
+    <t>拆除多余防护板以减轻重量的工作安全靴。</t>
+  </si>
+  <si>
+    <t>配备小型驱动装置、能够辅助穿戴者行走的工作靴。本来用于搬运重物，在快速移动时也意外地好用。</t>
+  </si>
+  <si>
+    <t>軽量安全靴</t>
+  </si>
+  <si>
+    <t>動力補助ブーツ</t>
+  </si>
+  <si>
+    <t>不要な保護板を取り外し、軽量化した作業用安全靴</t>
+  </si>
+  <si>
+    <t>小型駆動装置が装着者の歩行を補助する作業用ブーツ。重量物の運搬用に作られたが、素早く移動する時にも意外と役に立つ。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1382,6 +1913,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1436,7 +1974,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1650,7 +2188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -1718,407 +2256,506 @@
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+      <c r="B6" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>341</v>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -2129,7 +2766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -2153,10 +2790,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -2164,10 +2801,10 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -2175,10 +2812,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -2186,10 +2823,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -2197,406 +2834,505 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>342</v>
+        <v>321</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>343</v>
+        <v>323</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>337</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>356</v>
+        <v>325</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>350</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>344</v>
+        <v>327</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>345</v>
+        <v>329</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>362</v>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -2607,7 +3343,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -2631,10 +3367,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -2642,10 +3378,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -2653,10 +3389,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -2664,10 +3400,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -2675,406 +3411,505 @@
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" s="6" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>358</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>365</v>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -3085,7 +3920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -3109,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -3120,10 +3955,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -3131,10 +3966,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -3142,10 +3977,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -3153,406 +3988,505 @@
         <v>15</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C20" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C24" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B25" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.45">
       <c r="A27" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C27" s="8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>371</v>
+      <c r="B44" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A5CBEC-FC58-41D8-9CA1-3C129A91A950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69564FED-A211-4978-95DC-BB8A2E1A9933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="471">
   <si>
     <t>itemId</t>
   </si>
@@ -1839,6 +1839,103 @@
   </si>
   <si>
     <t>小型駆動装置が装着者の歩行を補助する作業用ブーツ。重量物の運搬用に作られたが、素早く移動する時にも意外と役に立つ。</t>
+  </si>
+  <si>
+    <t>item.relic.overclockcore</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버클럭 코어</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.relic.scrapcompactor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고철 압축기</t>
+  </si>
+  <si>
+    <t>파괴된 기계의 잔해를 압축해 재활용하는 장치입니다. 전장에는 원료가 넘쳐납니다.</t>
+  </si>
+  <si>
+    <t>안전 한계를 무시하고 출력을 끌어올리는 개조 동력 코어입니다. 성능을 얻는 데에는 언제나 대가가 따릅니다.</t>
+  </si>
+  <si>
+    <t>Scrap Compactor</t>
+  </si>
+  <si>
+    <t>Overclock Core</t>
+  </si>
+  <si>
+    <t>A device that compresses and recycles debris from destroyed machines. The battlefield provides no shortage of raw material.</t>
+  </si>
+  <si>
+    <t>A modified power core that pushes its output beyond safe limits. Greater performance always comes at a cost.</t>
+  </si>
+  <si>
+    <t>スクラップ圧縮機</t>
+  </si>
+  <si>
+    <t>オーバークロックコア</t>
+  </si>
+  <si>
+    <t>破壊された機械の残骸を圧縮し、再利用する装置。戦場なら原料に困ることはない。</t>
+  </si>
+  <si>
+    <t>安全限界を無視して出力を引き上げる改造動力コア。性能を得るには、常に代償が伴う。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>废</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>压缩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>机</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>超频核心</t>
+  </si>
+  <si>
+    <t>将被摧毁机械的残骸压缩并回收利用的装置。在战场上，从来不缺原料。</t>
+  </si>
+  <si>
+    <t>无视安全极限、强行提升输出的改造动力核心。更高的性能总要付出代价。</t>
   </si>
 </sst>
 </file>
@@ -2188,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -2758,6 +2855,28 @@
         <v>422</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2766,7 +2885,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38.3984375" style="1" bestFit="1" customWidth="1"/>
@@ -3335,6 +3454,28 @@
         <v>433</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3343,7 +3484,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -3912,6 +4053,28 @@
         <v>452</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>466</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3920,7 +4083,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -4489,6 +4652,28 @@
         <v>448</v>
       </c>
     </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>470</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Ra95497a95a4a4564"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R673f452c9db4483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R8243de49e69942f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R92513f7d535e419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rc3cce7102b364281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R1adce2aeec6840c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="Rd62fcc07aae2446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rf3945ea7ab964fc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4676,6 +4676,105 @@
         <x:v>봉인된 특이점 코어를 사용하는 중화기입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>item.weapon.rifle.smilesignal</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>스마일 시그널</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>거너의 색과 얼굴 스티커를 담아 제작한 전용 에너지 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>item.weapon.rifle.dustsparrow</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>모래 참새</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>모래 먼지 속에서도 안정적으로 작동하는 경량 일체형 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>item.weapon.grenadelauncher.pulsecask</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>펄스 챔버</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>밀폐된 펄스 챔버로 에너지를 압축하는 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>item.weapon.rifle.glassrail</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>유리빛 궤도</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>투명 덮개 속 단일 에너지 도관을 사용하는 정밀 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>item.weapon.shotgun.embercoil</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>잔불 고리</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>열차폐판 안쪽의 잔불 코일을 순간적으로 방출하는 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>item.weapon.grenadelauncher.halomortar</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>헤일로 박격포</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>밀폐된 환형 투사기로 탄도를 안정시키는 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>item.weapon.shotgun.echovault</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>에코 챔버</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>직선형 공명실에 충격파를 축적하는 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>item.weapon.grenadelauncher.sunfallengine</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>일식 기관</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>태양 코어의 열을 한 덩어리로 압축해 발사하는 중화기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>item.weapon.shotgun.starforgebreach</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>스타 브리처</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>제련 코어의 에너지를 넓은 총구로 방출하는 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5999,6 +6098,105 @@
         <x:v>A heavy weapon powered by a sealed singularity core.</x:v>
       </x:c>
     </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>item.weapon.rifle.smilesignal</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Smile Signal</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>A signature energy rifle finished in the Gunner's colors and marked with her face sticker.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>item.weapon.rifle.dustsparrow</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Dust Sparrow</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>A lightweight integrated rifle built to operate reliably through blowing sand.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>item.weapon.grenadelauncher.pulsecask</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Pulse Chamber</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>A grenade launcher that compresses energy inside a sealed pulse chamber.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>item.weapon.rifle.glassrail</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Glass Rail</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>A precision rifle driven by a single energy conduit beneath a transparent cover.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>item.weapon.shotgun.embercoil</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Ember Coil</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>A shotgun that releases the ember coil sealed beneath its heat shielding.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>item.weapon.grenadelauncher.halomortar</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Halo Mortar</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>A grenade launcher that stabilizes its trajectory with a sealed annular projector.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>item.weapon.shotgun.echovault</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Echo Chamber</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>A shotgun that stores shockwaves inside a straight resonance chamber.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>item.weapon.grenadelauncher.sunfallengine</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Sunfall Engine</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>A heavy launcher that compresses a solar core's heat into a single discharge.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>item.weapon.shotgun.starforgebreach</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Star Breacher</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>A shotgun that vents the energy of its forge core through a broad muzzle.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7322,6 +7520,105 @@
         <x:v>封印された特異点コアを動力源とする重火器です。</x:v>
       </x:c>
     </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>item.weapon.rifle.smilesignal</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>スマイルシグナル</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>ガンナーのカラーとフェイスステッカーをあしらった専用エネルギーライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>item.weapon.rifle.dustsparrow</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>サンドスパロー</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>砂塵の中でも安定して作動する軽量一体型ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>item.weapon.grenadelauncher.pulsecask</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>パルスチャンバー</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>密閉パルスチャンバーでエネルギーを圧縮するグレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>item.weapon.rifle.glassrail</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>グラスレール</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>透明カバー内の単一エネルギー導管を使う精密ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>item.weapon.shotgun.embercoil</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>エンバーコイル</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>遮熱板の内側に封じた残火コイルを瞬時に放出するショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>item.weapon.grenadelauncher.halomortar</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>ヘイロー迫撃砲</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>密閉型の環状投射器で弾道を安定させるグレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>item.weapon.shotgun.echovault</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>エコーチャンバー</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>直線型の共鳴室に衝撃波を蓄えるショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>item.weapon.grenadelauncher.sunfallengine</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>サンフォール・エンジン</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>太陽コアの熱を一塊に圧縮して放つ重火器です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>item.weapon.shotgun.starforgebreach</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>スター・ブリーチャー</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>鍛造コアのエネルギーを幅広い銃口から放出するショットガンです。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8645,6 +8942,105 @@
         <x:v>以封存的奇点核心为动力的重型武器。</x:v>
       </x:c>
     </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>item.weapon.rifle.smilesignal</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>微笑信号</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>采用枪手配色并饰有其头像贴纸的专属能量步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>item.weapon.rifle.dustsparrow</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>沙尘雀</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>可在风沙中稳定运作的轻量一体式步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>item.weapon.grenadelauncher.pulsecask</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>脉冲舱</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>利用密封脉冲舱压缩能量的榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>item.weapon.rifle.glassrail</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>琉光轨道</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>采用透明护罩内单一能量导管的精密步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>item.weapon.shotgun.embercoil</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>余烬环</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>瞬间释放封存在隔热板内余烬线圈能量的霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>item.weapon.grenadelauncher.halomortar</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>光环迫击炮</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>通过密封环形投射器稳定弹道的榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>item.weapon.shotgun.echovault</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>回声舱</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>在直线共鸣舱内蓄积冲击波的霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>item.weapon.grenadelauncher.sunfallengine</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>日蚀机芯</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>将太阳核心热量压缩后一次释放的重型发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>item.weapon.shotgun.starforgebreach</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>星锻突破者</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>通过宽阔枪口释放锻炉核心能量的霰弹枪。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rc3cce7102b364281"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R1adce2aeec6840c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="Rd62fcc07aae2446a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rf3945ea7ab964fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rf3640a4a7a25450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rbeb9e6615201474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R00f7c5c29c1c4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rdef942a9fcc8434d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4775,6 +4775,193 @@
         <x:v>제련 코어의 에너지를 넓은 총구로 방출하는 산탄총입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>item.weapon.shotgun.voidbarrage</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>공허 연발포</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>다중 공진 총구가 공허 전하를 한꺼번에 토해내는 중형 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>item.weapon.shotgun.redlinebreacher</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>레드라인 브리처</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>주황색 충격 완충부와 수동 펌프를 갖춘 신뢰성 높은 제압용 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>item.weapon.shotgun.goldentwinstar</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>황금 쌍성</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>황금 장갑 아래 두 개의 포신을 나란히 묶은 고출력 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>item.weapon.shotgun.magmacrusher</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>용암 파쇄포</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>용융 열이 갈라진 외피 사이로 새어 나오는 근접 파쇄용 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>item.weapon.shotgun.whiterefrigerant</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>백색 냉매</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>백색 외장과 냉각 앰풀로 반동열을 제어하는 경량 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>item.weapon.shotgun.thundercoil</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>뇌전 코일</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>청색 코일에 전하를 축적해 산탄과 함께 방전하는 전자 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>item.weapon.shotgun.scrapdrum</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>고철 탄통</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>폐공장 탄통과 배관을 이어 붙인 짧고 튼튼한 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>item.weapon.rifle.ioncascade</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>이온 폭포</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>백색 프레임의 대형 이온 코어를 연속 순환시키는 에너지 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>item.weapon.rifle.nightwarden</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>야간 감시자</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>빛을 억제한 녹색 외장과 소형 표적등을 갖춘 잠입용 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>item.weapon.rifle.workspark</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>공업 스파크</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>건설 장비의 안전색과 고출력 모터를 재사용한 산업용 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>item.weapon.rifle.rusthound</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>녹슨 사냥개</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>녹슨 부품과 노출 배선을 엮어 만든 집요한 생존형 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>item.weapon.rifle.siegeframe</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>공성 프레임</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>중장갑 프레임과 대형 총열로 지속 화력을 견디는 군용 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>item.weapon.rifle.emberline</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>잔불 선로</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>주황색 에너지 셀을 직선으로 배열해 열 방출을 안정시킨 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>item.weapon.rifle.whitenoise</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>백색 소음</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>불필요한 장식을 줄인 백색 프레임의 장거리 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>item.weapon.rifle.arcvector</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>아크 벡터</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>청록 전류가 총열을 따라 정렬되도록 설계된 고속 에너지 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>item.weapon.rifle.bluehorizon</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>푸른 지평선</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>푸른 에너지 노심과 정밀 조준계를 결합한 최상급 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>item.weapon.rifle.redsingularity</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>적색 특이점</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>적색 코일이 특이점 전하를 집속하는 실험형 중형 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6197,6 +6384,193 @@
         <x:v>A shotgun that vents the energy of its forge core through a broad muzzle.</x:v>
       </x:c>
     </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>item.weapon.shotgun.voidbarrage</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Void Barrage</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>A heavy shotgun whose clustered resonance muzzles unleash void charge in a single barrage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>item.weapon.shotgun.redlinebreacher</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>Redline Breacher</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>A reliable breaching shotgun with an orange recoil shroud and manual pump.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>item.weapon.shotgun.goldentwinstar</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>Golden Twin Star</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>A high-output shotgun binding two barrels beneath gold armor.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>item.weapon.shotgun.magmacrusher</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>Magma Crusher</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>A close-range breaching shotgun that vents molten heat through its cracked shell.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>item.weapon.shotgun.whiterefrigerant</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>White Refrigerant</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>A lightweight shotgun that controls recoil heat with a white shell and coolant ampoules.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>item.weapon.shotgun.thundercoil</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>Thunder Coil</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>An electro-shotgun that stores charge in blue coils and discharges it with every blast.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>item.weapon.shotgun.scrapdrum</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>Scrap Drum</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>A short, rugged shotgun assembled from factory drums and discarded piping.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>item.weapon.rifle.ioncascade</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>Ion Cascade</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>An energy rifle that continuously cycles a large ion core through its white frame.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>item.weapon.rifle.nightwarden</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>Night Warden</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>A covert rifle with light-suppressing green armor and compact target lamps.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>item.weapon.rifle.workspark</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>Workspark</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>An industrial rifle reusing construction safety colors and a high-output motor.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>item.weapon.rifle.rusthound</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>Rust Hound</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>A relentless survival rifle woven from rusted parts and exposed wiring.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>item.weapon.rifle.siegeframe</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>Siege Frame</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>A military rifle built around heavy armor and a large barrel for sustained fire.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>item.weapon.rifle.emberline</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>Ember Line</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>A rifle whose in-line orange energy cells stabilize heat discharge.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>item.weapon.rifle.whitenoise</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>White Noise</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>A long-range rifle built on a clean white frame with all excess ornament removed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>item.weapon.rifle.arcvector</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>Arc Vector</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>A high-speed energy rifle designed to align cyan current along its barrel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>item.weapon.rifle.bluehorizon</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>Blue Horizon</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>A top-grade rifle combining a blue energy core with precision optics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>item.weapon.rifle.redsingularity</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>Red Singularity</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>An experimental heavy rifle whose red coils focus singularity charge.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7619,6 +7993,193 @@
         <x:v>鍛造コアのエネルギーを幅広い銃口から放出するショットガンです。</x:v>
       </x:c>
     </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>item.weapon.shotgun.voidbarrage</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>ヴォイド・バラージ</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>複数の共鳴銃口から虚空電荷を一斉放出する重型ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>item.weapon.shotgun.redlinebreacher</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>レッドライン・ブリーチャー</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>橙色の反動緩衝部と手動ポンプを備えた信頼性の高い制圧用ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>item.weapon.shotgun.goldentwinstar</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>黄金の双星</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>黄金装甲の下に二本の銃身を並べた高出力ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>item.weapon.shotgun.magmacrusher</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>マグマクラッシャー</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>亀裂の入った外殻から溶融熱を放つ近距離破砕用ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>item.weapon.shotgun.whiterefrigerant</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>白色冷媒</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>白い外装と冷却アンプルで反動熱を制御する軽量ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>item.weapon.shotgun.thundercoil</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>雷電コイル</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>青いコイルに電荷を蓄え、散弾と同時に放電する電磁ショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>item.weapon.shotgun.scrapdrum</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>スクラップドラム</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>廃工場の弾倉と配管をつないで作った短く頑丈なショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>item.weapon.rifle.ioncascade</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>イオンカスケード</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>白いフレームの大型イオンコアを連続循環させるエネルギーライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>item.weapon.rifle.nightwarden</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>ナイトウォーデン</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>光を抑える緑色装甲と小型照準灯を備えた潜入用ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>item.weapon.rifle.workspark</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>ワークスパーク</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>建設機械の安全色と高出力モーターを再利用した産業用ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>item.weapon.rifle.rusthound</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>ラストハウンド</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>錆びた部品と露出配線を組み上げた執念深い生存型ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>item.weapon.rifle.siegeframe</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>シージフレーム</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>重装甲フレームと大型銃身で持続射撃に耐える軍用ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>item.weapon.rifle.emberline</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>エンバーライン</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>橙色のエネルギーセルを直列配置し、排熱を安定させたライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>item.weapon.rifle.whitenoise</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>ホワイトノイズ</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>余分な装飾を排した白色フレームの長距離ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>item.weapon.rifle.arcvector</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>アークベクター</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>青緑色の電流を銃身に沿って整列させる高速エネルギーライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>item.weapon.rifle.bluehorizon</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>ブルーホライズン</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>青いエネルギー炉心と精密照準器を組み合わせた最上級ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>item.weapon.rifle.redsingularity</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>レッドシンギュラリティ</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>赤いコイルで特異点電荷を集束する実験型重ライフルです。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9041,6 +9602,193 @@
         <x:v>通过宽阔枪口释放锻炉核心能量的霰弹枪。</x:v>
       </x:c>
     </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>item.weapon.shotgun.voidbarrage</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>虚空齐射</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>通过多重共振枪口一次释放虚空电荷的重型霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>item.weapon.shotgun.redlinebreacher</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>红线破门者</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>配备橙色后坐缓冲罩和手动泵动机构的可靠压制霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>item.weapon.shotgun.goldentwinstar</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>黄金双星</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>在金色装甲下并列两根枪管的高功率霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>item.weapon.shotgun.magmacrusher</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>熔岩粉碎者</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>从龟裂外壳中释放熔融热量的近距离破门霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>item.weapon.shotgun.whiterefrigerant</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>白色冷媒</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>利用白色外壳和冷却安瓿控制后坐热量的轻型霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>item.weapon.shotgun.thundercoil</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>雷霆线圈</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>将电荷储存在蓝色线圈中并随霰弹一同释放的电磁霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>item.weapon.shotgun.scrapdrum</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>废铁弹鼓</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>用废弃工厂弹鼓和管道拼装而成的短小坚固霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>item.weapon.rifle.ioncascade</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>离子瀑流</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>让大型离子核心在白色框架中持续循环的能量步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>item.weapon.rifle.nightwarden</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>夜间守望者</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>配备抑光绿色装甲和小型瞄准灯的潜入步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>item.weapon.rifle.workspark</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>工造火花</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>复用工程机械安全色和高功率马达的工业步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>item.weapon.rifle.rusthound</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>锈蚀猎犬</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>由锈蚀零件和外露线缆组装而成的顽强生存型步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>item.weapon.rifle.siegeframe</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>攻城框架</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>以重装甲框架和大型枪管承受持续射击的军用步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>item.weapon.rifle.emberline</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>余烬阵列</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>将橙色能量电池直线排列以稳定散热的步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>item.weapon.rifle.whitenoise</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>白噪声</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>去除多余装饰、采用白色框架的远程步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>item.weapon.rifle.arcvector</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>电弧矢量</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>让青色电流沿枪管整齐流动的高速能量步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>item.weapon.rifle.bluehorizon</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>蔚蓝地平线</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>结合蓝色能量核心与精密瞄具的顶级步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>item.weapon.rifle.redsingularity</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>赤红奇点</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>以红色线圈聚焦奇点电荷的实验型重步枪。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rf3640a4a7a25450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rbeb9e6615201474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R00f7c5c29c1c4796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rdef942a9fcc8434d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rc697b9739e654f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rf2c54536ad0b47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="Rd2ab4aafc87844a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rf09f1750dd464db3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4962,6 +4962,138 @@
         <x:v>적색 코일이 특이점 전하를 집속하는 실험형 중형 라이플입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>item.weapon.shotgun.dockbreaker</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>부두의 철퇴</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>부두 계류 장비를 충격파 산탄총으로 개조했습니다. 닻을 닮은 넓은 총구가 반동을 붙잡습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>item.weapon.rifle.phaseorchid</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>허공에 핀 난초</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>다크 제이드 장갑 사이로 자홍빛 에너지가 피어나는 의전용 정밀 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>item.weapon.rifle.massproduced</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>양산형 라이플</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>규격 부품으로 대량 생산된 표준형 에너지 라이플입니다. 화려하진 않지만 어디서나 같은 성능을 냅니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>item.weapon.shotgun.homesafety</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>가정용 안전 용품</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>가정용 충격 억제 장치를 산탄총으로 개조했습니다. 비살상이라는 표시는 오래전에 지워졌습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>item.weapon.rifle.fieldmod</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>개조된 라이플</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>현장에서 주운 패널과 방열판을 덧대 성능을 끌어올린 개조형 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>item.weapon.rifle.outdoorhunter</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>아웃도어 헌팅 라이플</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>목재 모방 소재와 에너지 총열을 결합한 장거리 사냥용 라이플입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>item.weapon.grenadelauncher.fireworks</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>폭죽놀이</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>다색 탄두를 차례로 점화해 전장을 축제처럼 밝히는 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>item.weapon.shotgun.sulbing</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>설빙</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>넓은 냉각 총구로 압축 냉기를 한꺼번에 방출하는 산탄총입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>item.weapon.grenadelauncher.glasscannon</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>유리대포</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>투명 덮개 안의 취약한 고출력 코어를 한계까지 밀어붙인 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>item.weapon.shotgun.incinerator</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>소각 산탄총</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>폐기물 소각로의 압력 챔버를 개조해 불길을 산탄처럼 쏟아내는 중화기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>item.weapon.grenadelauncher.apocalypse</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>묵시록적 파괴</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>여러 개의 봉인 코어가 순차 붕괴하며 종말급 충격을 만드는 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>item.weapon.shotgun.conversationstarter</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>훌륭한 대화수단</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>대화가 통하지 않을 때 꺼내는 거대한 일체형 충격파 산탄 장비입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6571,6 +6703,138 @@
         <x:v>An experimental heavy rifle whose red coils focus singularity charge.</x:v>
       </x:c>
     </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>item.weapon.shotgun.dockbreaker</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>Dockbreaker</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>A dock-mooring assembly rebuilt as a shockwave shotgun. Its anchor-shaped muzzle braces the recoil.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>item.weapon.rifle.phaseorchid</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>Phase Orchid</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>A ceremonial precision rifle where magenta energy blooms between dark-jade armor plates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>item.weapon.rifle.massproduced</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>Mass-Produced Rifle</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>A standard energy rifle built from interchangeable factory parts. It is plain, but performs the same everywhere.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>item.weapon.shotgun.homesafety</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>Home Safety Device</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>A household impact suppressor converted into a shotgun. The non-lethal label was removed long ago.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>item.weapon.rifle.fieldmod</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>Field-Mod Rifle</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>A modified rifle upgraded in the field with scavenged panels and heat shields.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>item.weapon.rifle.outdoorhunter</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>Outdoor Hunting Rifle</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>A long-range hunting rifle combining synthetic wood trim with a futuristic energy barrel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>item.weapon.grenadelauncher.fireworks</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>Fireworks</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>A grenade launcher that ignites multicolored warheads in sequence and lights the battlefield like a festival.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>item.weapon.shotgun.sulbing</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>Seolbing</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>A shotgun that releases compressed cold through a wide refrigeration muzzle.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>item.weapon.grenadelauncher.glasscannon</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>Glass Cannon</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>A grenade launcher that pushes a fragile high-output core beneath a transparent cover to its limit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>item.weapon.shotgun.incinerator</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>Incinerator Shotgun</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>A heavy weapon rebuilt from a waste-incinerator pressure chamber to pour fire like buckshot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>item.weapon.grenadelauncher.apocalypse</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>Apocalyptic Destruction</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>A grenade launcher whose multiple sealed cores collapse in sequence to create an apocalyptic impact.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>item.weapon.shotgun.conversationstarter</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>A Fine Conversation Starter</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>A massive monolithic shockwave shotgun brought out when words stop working.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8180,6 +8444,138 @@
         <x:v>赤いコイルで特異点電荷を集束する実験型重ライフルです。</x:v>
       </x:c>
     </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>item.weapon.shotgun.dockbreaker</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>波止場の鉄槌</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>波止場の係留装置を衝撃波ショットガンへ改造しました。錨形の広い銃口が反動を受け止めます。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>item.weapon.rifle.phaseorchid</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>虚空に咲く蘭</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>ダークジェイドの装甲の間に紅紫のエネルギーが咲く、儀礼用精密ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>item.weapon.rifle.massproduced</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>量産型ライフル</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>規格部品で大量生産された標準型エネルギーライフルです。華美ではありませんが、どこでも同じ性能を発揮します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>item.weapon.shotgun.homesafety</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>家庭用安全装置</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>家庭用衝撃抑制装置をショットガンへ改造しました。非殺傷という表示はとうに消されています。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>item.weapon.rifle.fieldmod</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>現地改修ライフル</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>現地で拾ったパネルと放熱板を追加し、性能を引き上げた改修型ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>item.weapon.rifle.outdoorhunter</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>アウトドア・ハンティングライフル</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>木材模倣素材と未来型エネルギー銃身を組み合わせた長距離狩猟用ライフルです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>item.weapon.grenadelauncher.fireworks</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>花火遊び</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>多色弾頭を順番に点火し、戦場を祭りのように照らすグレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>item.weapon.shotgun.sulbing</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>雪氷</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>広い冷却銃口から圧縮冷気を一気に放出するショットガンです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>item.weapon.grenadelauncher.glasscannon</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>ガラスの大砲</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>透明カバー内の脆い高出力コアを限界まで駆動するグレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>item.weapon.shotgun.incinerator</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>焼却ショットガン</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>廃棄物焼却炉の圧力室を改造し、炎を散弾のように浴びせる重火器です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>item.weapon.grenadelauncher.apocalypse</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>黙示録の破壊</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>複数の封印コアが順次崩壊し、終末級の衝撃を生むグレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>item.weapon.shotgun.conversationstarter</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>素晴らしい対話手段</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>話が通じない時に取り出す、巨大な一体型衝撃波ショットガンです。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9789,6 +10185,138 @@
         <x:v>以红色线圈聚焦奇点电荷的实验型重步枪。</x:v>
       </x:c>
     </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>item.weapon.shotgun.dockbreaker</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>码头铁锤</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>由码头系泊装置改造而成的冲击波霰弹枪，锚形宽口能够稳住后坐力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>item.weapon.rifle.phaseorchid</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>虚空兰花</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>暗玉色装甲之间绽放着品红能量的礼仪型精密步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>item.weapon.rifle.massproduced</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>量产型步枪</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>使用标准零件批量生产的制式能量步枪。外表朴素，却能在任何地方保持稳定性能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>item.weapon.shotgun.homesafety</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>家用安全设备</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>由家用冲击抑制装置改造成的霰弹枪，非致命标签早已被抹去。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>item.weapon.rifle.fieldmod</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>战地改装步枪</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>加装战场上搜集的面板与散热板，以提升性能的改装型步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>item.weapon.rifle.outdoorhunter</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>户外狩猎步枪</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>结合仿木材质与未来能量枪管的远程狩猎步枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>item.weapon.grenadelauncher.fireworks</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>烟花游戏</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>依次点燃彩色弹头，把战场照得如同庆典的榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>item.weapon.shotgun.sulbing</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>雪冰</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>通过宽阔制冷枪口一次释放压缩寒气的霰弹枪。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>item.weapon.grenadelauncher.glasscannon</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>玻璃大炮</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>把透明护罩内脆弱的高输出核心推至极限的榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>item.weapon.shotgun.incinerator</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>焚化霰弹枪</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>由废弃物焚化炉压力舱改造而成，能像霰弹一样倾泻火焰的重武器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>item.weapon.grenadelauncher.apocalypse</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>末日毁灭</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>多个封印核心依次崩溃，制造末日级冲击的榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>item.weapon.shotgun.conversationstarter</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>绝佳的沟通手段</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>当语言失去作用时才会拿出的巨型一体式冲击波霰弹枪。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="Rc697b9739e654f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="Rf2c54536ad0b47bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="Rd2ab4aafc87844a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rf09f1750dd464db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R1054f281c46c4df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R0451ad942ef44357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R732bf9e5bd02428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R7cafe87e8f7e4236"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5094,6 +5094,72 @@
         <x:v>대화가 통하지 않을 때 꺼내는 거대한 일체형 충격파 산탄 장비입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>당근칼</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>장난감처럼 귀엽지만 양손으로 휘둘러야 하는 큼직한 당근 모양 대검입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>탄두 배달부</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>공장 물류용 공압 실린더를 단발식 유탄발사기로 개조했습니다. 단순하지만 탄두는 정확히 배달합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>바운스 버디</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>둥근 고무 완충통과 청록색 조준등을 단 소형 유탄발사기입니다. 통통 튀는 외형이 반동을 부드럽게 받아냅니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>고철 호퍼</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>폐기된 광물 호퍼와 작업장 배관을 이어 붙인 드럼식 유탄발사기입니다. 묵직한 골격이 발사 흔들림을 잡아줍니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>클러스터 팝</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>세 개의 소형 캡슐을 하나의 탄두로 묶어 발사 순서를 안정화한 고급 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>스마트 퓨즈</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>비행 거리를 계산해 탄두의 기폭 시간을 조절하는 프로그래머블 유탄발사기입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6835,6 +6901,72 @@
         <x:v>A massive monolithic shockwave shotgun brought out when words stop working.</x:v>
       </x:c>
     </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>Carrot Greatsword</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>A cute carrot-shaped greatsword that looks like a toy but takes both hands to swing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>Shell Courier</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>A factory logistics pneumatic cylinder rebuilt as a single-shot grenade launcher. Simple, but it delivers every shell on target.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>Bounce Buddy</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>A compact grenade launcher with a rounded rubber buffer and teal sight light. Its springy frame softens the recoil.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>Scrap Hopper</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>A drum-fed grenade launcher assembled from a discarded ore hopper and workshop piping. Its heavy frame keeps each shot steady.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>Cluster Pop</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>An advanced grenade launcher that binds three compact capsules into one shell and stabilizes their firing sequence.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>Smart Fuse</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>A programmable grenade launcher that calculates flight distance and adjusts each shell's detonation timing.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8576,6 +8708,72 @@
         <x:v>話が通じない時に取り出す、巨大な一体型衝撃波ショットガンです。</x:v>
       </x:c>
     </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>にんじん大剣</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>おもちゃのようにかわいい見た目ですが、両手で振るう大きなにんじん型の大剣です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>弾頭の配達人</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>工場物流用の空圧シリンダーを単発式グレネードランチャーに改造しました。単純ですが、弾頭は正確に届けます。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>バウンス・バディ</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>丸いゴム製バッファーと青緑色の照準灯を備えた小型グレネードランチャーです。弾むような外装が反動を和らげます。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>スクラップ・ホッパー</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>廃棄された鉱石ホッパーと作業場の配管をつないだドラム式グレネードランチャーです。重い骨格が射撃のぶれを抑えます。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>クラスター・ポップ</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>三つの小型カプセルを一つの弾頭に束ね、発射順序を安定させた上級グレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>スマート・ヒューズ</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>飛翔距離を計算し、弾頭の起爆時間を調整するプログラマブル・グレネードランチャーです。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10317,6 +10515,72 @@
         <x:v>当语言失去作用时才会拿出的巨型一体式冲击波霰弹枪。</x:v>
       </x:c>
     </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>胡萝卜大剑</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>外形像玩具一样可爱，但必须双手挥动的巨大胡萝卜造型大剑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>弹头快递员</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>由工厂物流用气压缸改造成的单发榴弹发射器。结构简单，却能把弹头准确送达。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>弹跳伙伴</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>配有圆形橡胶缓冲筒与青绿色瞄准灯的小型榴弹发射器。富有弹性的外壳能柔和吸收后坐力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>废铁料斗</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>把废弃矿石料斗与工坊管道拼装而成的鼓式榴弹发射器。厚重骨架能够抑制射击晃动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>集束爆弹</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>把三枚小型胶囊组合成一枚弹头，并稳定其发射顺序的高级榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>智能引信</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>能够计算飞行距离并调整弹头起爆时间的可编程榴弹发射器。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -4899,7 +4899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -6709,6 +6709,23 @@
         <v>1464</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.relic.manarelay</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마나 중계기</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주변 동료에게 회복 에너지를 전달하는 휴대용 중계 장치입니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6717,7 +6734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38.3984375" style="1" customWidth="1"/>
@@ -8529,6 +8546,23 @@
         <v>1466</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.relic.manarelay</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana Relay</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A portable relay that shares recovery energy with nearby allies.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8537,7 +8571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -10349,6 +10383,23 @@
         <v>1460</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.relic.manarelay</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マナ中継器</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周囲の仲間へ回復エネルギーを届ける携帯中継装置です。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10357,7 +10408,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="36.796875" style="1" customWidth="1"/>
@@ -12169,6 +12220,23 @@
         <v>1462</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.relic.manarelay</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">法力中继器</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">向附近队友传递恢复能量的便携式中继装置。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="36.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -3248,6 +3248,176 @@
       <c r="C165" s="0" t="inlineStr">
         <is>
           <t>주변 동료에게 회복 에너지를 전달하는 휴대용 중계 장치입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.dampingcore</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>진동 감쇠 코어</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>지면 충격을 흡수해 스킬 출력으로 되돌리는 코어입니다. 대신 마나 순환이 둔해집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.overloadheart</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>과부하 심장</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>쓰러뜨린 기계의 잔류 전력을 빨아들여 각성 회로를 강제로 다시 돌립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.chargecircuit</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>충전 회로</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>처치 순간의 전류를 다음 사격용 축전지로 곧장 보내는 우회 회로입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.targetlens</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>표적 분석 렌즈</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>표식이 남긴 신호를 읽어 장갑의 이음매를 짚어 주는 조준 렌즈입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.manaconverter</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>마나 변환기</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>스킬을 쓰고 남은 마나 파동을 무기 출력으로 바꿔 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.sparebattery</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>보조 배터리</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>어디서 주웠는지 모를 휴대용 배터리입니다. 아직 눈금이 가득합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.elementresonator</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>원소 공명기</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>서로 다른 원소가 한 점에서 겹치면 그 자리를 터뜨리는 불안정한 공명 장치입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.adrenalineinjector</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>아드레날린 주입기</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>전투 신호를 받으면 정량보다 조금 많이 주입합니다. 조금만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.heatexchanger</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>열교환 헬멧</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>머리 위에서 열과 냉기, 전류를 순환시켜 스킬 회로를 안정시킵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.chest.coolantarmor</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>냉각수 순환 갑주</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>스킬의 반동열을 냉각수 관으로 흘려보내며 그 흐름으로 마나를 끌어올립니다.</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="38.3984375" customWidth="1" style="1" min="1" max="1"/>
@@ -6072,6 +6242,176 @@
       <c r="C165" s="0" t="inlineStr">
         <is>
           <t>A portable relay that shares recovery energy with nearby allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.dampingcore</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>Vibration Damping Core</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>A core that absorbs ground impact and feeds it back into skill output, at the cost of slower mana flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.overloadheart</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>Overload Heart</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>Drains residual power from destroyed machines to force the awakening circuit back online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.chargecircuit</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>Charge Circuit</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>A bypass circuit that routes the current from each kill straight into the next shot's capacitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.targetlens</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>Target Analysis Lens</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>A targeting lens that reads the signal left by marks and points out the seams in the armor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.manaconverter</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>Mana Converter</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>Converts the leftover mana surge from skills into weapon output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.sparebattery</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>Spare Battery</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>A portable battery of unknown origin. The gauge is still full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.elementresonator</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>Element Resonator</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>An unstable resonance device that detonates the spot where two different elements overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.adrenalineinjector</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>Adrenaline Injector</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>Injects a little more than the recommended dose whenever combat starts. Just a little.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.heatexchanger</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>Heat Exchanger Helmet</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>Circulates heat, cold and current overhead to stabilize skill circuits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.chest.coolantarmor</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>Coolant Circulation Armor</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>Channels skill recoil heat through coolant lines and uses the flow to draw up mana.</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="36.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -8896,6 +9236,176 @@
       <c r="C165" s="0" t="inlineStr">
         <is>
           <t>周囲の仲間へ回復エネルギーを届ける携帯中継装置です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.dampingcore</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>振動減衰コア</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>地面の衝撃を吸収してスキル出力に還元するコアです。代わりにマナの循環が鈍くなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.overloadheart</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>過負荷の心臓</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>倒した機械の残留電力を吸い上げ、覚醒回路を強制的に再起動させます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.chargecircuit</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>充電回路</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>撃破の瞬間の電流を次の射撃用蓄電池へ直接送るバイパス回路です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.targetlens</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>標的分析レンズ</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>マーキングが残した信号を読み取り、装甲の継ぎ目を示す照準レンズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.manaconverter</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>マナ変換器</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>スキル使用後に残ったマナの波動を武器出力に変換します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.sparebattery</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>補助バッテリー</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>どこで拾ったか分からない携帯用バッテリーです。目盛りはまだ満タンです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.elementresonator</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>元素共鳴器</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>異なる元素が一点で重なると、その場所を爆発させる不安定な共鳴装置です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.adrenalineinjector</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>アドレナリン注入器</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>戦闘信号を受けると規定量より少し多めに注入します。少しだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.heatexchanger</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>熱交換ヘルメット</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>頭上で熱と冷気、電流を循環させてスキル回路を安定させます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.chest.coolantarmor</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>冷却水循環甲冑</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>スキルの反動熱を冷却水管へ流し、その流れでマナを引き上げます。</t>
         </is>
       </c>
     </row>
@@ -8910,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="36.796875" customWidth="1" style="1" min="1" max="1"/>
@@ -11723,6 +12233,176 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.dampingcore</t>
+        </is>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>减震核心</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>吸收地面冲击并转化为技能输出的核心，但法力循环会变慢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.overloadheart</t>
+        </is>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>过载之心</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>吸取被击毁机械的残余电力，强行重启觉醒回路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.chargecircuit</t>
+        </is>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>充能回路</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>将击杀瞬间的电流直接送往下一次射击电容的旁路回路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.targetlens</t>
+        </is>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>目标分析透镜</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>读取标记留下的信号、指出装甲接缝的瞄准透镜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.manaconverter</t>
+        </is>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>法力转换器</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>将施放技能后残留的法力波动转化为武器输出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.sparebattery</t>
+        </is>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>备用电池</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>不知从哪捡来的便携电池，电量刻度依然是满的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>item.relic.elementresonator</t>
+        </is>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>元素共鸣器</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>不同元素在一点重叠时便会将该处引爆的不稳定共鸣装置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.adrenalineinjector</t>
+        </is>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>肾上腺素注射器</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>收到战斗信号时会注射比规定剂量稍多一点的量。只多一点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.heatexchanger</t>
+        </is>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>热交换头盔</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>在头顶循环热量、寒气与电流，以稳定技能回路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>item.armor.chest.coolantarmor</t>
+        </is>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>冷却液循环甲胄</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>将技能反冲热量导入冷却管，并借助水流汲取法力。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataLabel.xlsx
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>서로 다른 원소가 한 점에서 겹치면 그 자리를 터뜨리는 불안정한 공명 장치입니다.</t>
+          <t>원소가 깃든 표적에 반응해 그 자리를 터뜨리는 불안정한 공명 장치입니다. 서로 다른 원소가 겹치면 더 크게 터집니다.</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>An unstable resonance device that detonates the spot where two different elements overlap.</t>
+          <t>An unstable resonance device that detonates targets carrying an element. It bursts harder where two different elements overlap.</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>異なる元素が一点で重なると、その場所を爆発させる不安定な共鳴装置です。</t>
+          <t>元素を帯びた標的に反応し、その場所を爆発させる不安定な共鳴装置です。異なる元素が重なると、さらに激しく爆発します。</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>不同元素在一点重叠时便会将该处引爆的不稳定共鸣装置。</t>
+          <t>会对带有元素的目标产生反应并将该处引爆的不稳定共鸣装置。不同元素重叠时爆炸更猛烈。</t>
         </is>
       </c>
     </row>
